--- a/data/trans_orig/AIRE_2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan la contaminación ambiental en su municipio o lugar de residencia en 2023</t>
+          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan la contaminación ambiental en su municipio o lugar de residencia en 2023 (tasa de respuesta: 99,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23252</t>
+          <t>24381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12767</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42013</t>
+          <t>41817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60503</t>
+          <t>60330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58650</t>
+          <t>58121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84604</t>
+          <t>82995</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54646</t>
+          <t>55043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79411</t>
+          <t>80017</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56225</t>
+          <t>55931</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75380</t>
+          <t>75593</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119525</t>
+          <t>118656</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>149482</t>
+          <t>149554</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13554</t>
+          <t>13634</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>31473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24163</t>
+          <t>24598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45106</t>
+          <t>45686</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5885</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17713</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12515</t>
+          <t>12928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>26848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62456</t>
+          <t>63189</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34575</t>
+          <t>35117</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55030</t>
+          <t>56246</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70947</t>
+          <t>72126</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109186</t>
+          <t>109378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65662</t>
+          <t>63413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101383</t>
+          <t>99915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72022</t>
+          <t>71056</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93565</t>
+          <t>94132</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143493</t>
+          <t>142103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185965</t>
+          <t>185356</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,85%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50664</t>
+          <t>51925</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82434</t>
+          <t>82806</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31031</t>
+          <t>31933</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50384</t>
+          <t>51015</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90156</t>
+          <t>87615</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125652</t>
+          <t>125969</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>17109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>20252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13770</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13016</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32949</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52419</t>
+          <t>52421</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43935</t>
+          <t>43570</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61745</t>
+          <t>61719</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80150</t>
+          <t>81399</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108323</t>
+          <t>108146</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,3%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46172</t>
+          <t>45290</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67805</t>
+          <t>67474</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>37095</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54627</t>
+          <t>55303</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>88988</t>
+          <t>88088</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>116862</t>
+          <t>117860</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,92%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14814</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17879</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>14195</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28608</t>
+          <t>29881</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12872</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28297</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23551</t>
+          <t>24431</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28014</t>
+          <t>26702</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46863</t>
+          <t>45642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15593</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48232</t>
+          <t>46430</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24965</t>
+          <t>25706</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45094</t>
+          <t>46069</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47163</t>
+          <t>45440</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84184</t>
+          <t>84632</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12529</t>
+          <t>12186</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33081</t>
+          <t>32760</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26884</t>
+          <t>26888</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47665</t>
+          <t>49228</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43857</t>
+          <t>44455</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>73633</t>
+          <t>75891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22125</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48544</t>
+          <t>47630</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29208</t>
+          <t>28664</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41595</t>
+          <t>41290</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>70795</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13444</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15143</t>
+          <t>14597</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>22727</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45815</t>
+          <t>45257</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34308</t>
+          <t>34632</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53912</t>
+          <t>55459</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62719</t>
+          <t>63512</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>93165</t>
+          <t>93904</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>371</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>365</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17061</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26965</t>
+          <t>26511</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23642</t>
+          <t>24384</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37290</t>
+          <t>38016</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29271</t>
+          <t>29828</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38816</t>
+          <t>38631</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>36771</t>
+          <t>37406</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>47392</t>
+          <t>47506</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>69726</t>
+          <t>69253</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>83578</t>
+          <t>83725</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,23%</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,62 +3832,62 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>4336</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>4368</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>359</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>265</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>552</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>28263</t>
+          <t>28823</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>46279</t>
+          <t>47232</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>30550</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>46869</t>
+          <t>46483</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>63738</t>
+          <t>64636</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>88631</t>
+          <t>88367</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>39518</t>
+          <t>39592</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>58601</t>
+          <t>59025</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>42665</t>
+          <t>43208</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>59738</t>
+          <t>61670</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>87858</t>
+          <t>87311</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>115330</t>
+          <t>112921</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>14621</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10437</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>22928</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>23453</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>17739</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>20415</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>38044</t>
+          <t>37055</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18534</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>50705</t>
+          <t>49978</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>32879</t>
+          <t>33906</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>15536</t>
+          <t>14900</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>80852</t>
+          <t>79738</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>22539</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>43745</t>
+          <t>45902</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>89523</t>
+          <t>88246</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>358173</t>
+          <t>352706</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>111979</t>
+          <t>112636</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>463626</t>
+          <t>473798</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>80,16%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>73507</t>
+          <t>73667</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>109369</t>
+          <t>109111</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>23050</t>
+          <t>25572</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>194450</t>
+          <t>193985</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>73698</t>
+          <t>67136</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>288489</t>
+          <t>288686</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,84%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>42712</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>63752</t>
+          <t>67123</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>21254</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>93368</t>
+          <t>94468</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>23295</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>27952</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>41966</t>
+          <t>42969</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>10519</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>30087</t>
+          <t>31031</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>56064</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>44785</t>
+          <t>45153</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>70026</t>
+          <t>69453</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>81136</t>
+          <t>81224</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>116794</t>
+          <t>116872</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>61737</t>
+          <t>62055</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>89183</t>
+          <t>90711</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>53261</t>
+          <t>53047</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>76850</t>
+          <t>77459</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>121493</t>
+          <t>122153</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>159281</t>
+          <t>157771</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>105027</t>
+          <t>103335</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>137335</t>
+          <t>136112</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>98800</t>
+          <t>99360</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>126307</t>
+          <t>128233</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>212545</t>
+          <t>213442</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>257188</t>
+          <t>256889</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>32425</t>
+          <t>33029</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>54687</t>
+          <t>54724</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>54208</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>78826</t>
+          <t>78377</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>92519</t>
+          <t>91403</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>126255</t>
+          <t>124491</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>92388</t>
+          <t>91765</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>159074</t>
+          <t>155621</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>69427</t>
+          <t>63278</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>133233</t>
+          <t>130316</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>166409</t>
+          <t>167890</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>266998</t>
+          <t>269705</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>253830</t>
+          <t>255865</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>320807</t>
+          <t>320243</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>435819</t>
+          <t>433599</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>881134</t>
+          <t>927840</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>712041</t>
+          <t>709056</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1289526</t>
+          <t>1349015</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>436103</t>
+          <t>439416</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>511904</t>
+          <t>515582</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>275744</t>
+          <t>261939</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>502509</t>
+          <t>500321</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>687056</t>
+          <t>655904</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>987498</t>
+          <t>984342</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>168116</t>
+          <t>166042</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>218263</t>
+          <t>217935</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>117389</t>
+          <t>111900</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>224052</t>
+          <t>225418</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>287399</t>
+          <t>276518</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>423509</t>
+          <t>424557</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>119247</t>
+          <t>117195</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>160446</t>
+          <t>162978</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>110261</t>
+          <t>102194</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>205961</t>
+          <t>205036</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>228196</t>
+          <t>229033</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>343288</t>
+          <t>346830</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>845</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23428</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>460</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24381</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>36411</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>27011</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28683</t>
+          <t>46218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50450</t>
+          <t>62037</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41817</t>
+          <t>50857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60330</t>
+          <t>72868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>70080</t>
+          <t>98448</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58121</t>
+          <t>82409</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82995</t>
+          <t>112785</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68162</t>
+          <t>66951</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55043</t>
+          <t>56159</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80017</t>
+          <t>78926</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>66319</t>
+          <t>67573</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55931</t>
+          <t>57478</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75593</t>
+          <t>77425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>134482</t>
+          <t>134523</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118656</t>
+          <t>120512</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>149554</t>
+          <t>150698</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31473</t>
+          <t>28214</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12042</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17786</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>33652</t>
+          <t>30171</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24598</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45686</t>
+          <t>41409</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>16216</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>26090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>126529</t>
+          <t>136744</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126529</t>
+          <t>136744</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>126529</t>
+          <t>136744</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>138536</t>
+          <t>151180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138536</t>
+          <t>151180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>138536</t>
+          <t>151180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>265066</t>
+          <t>287923</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>265066</t>
+          <t>287923</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>265066</t>
+          <t>287923</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43161</t>
+          <t>41400</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29817</t>
+          <t>27367</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63189</t>
+          <t>58189</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44635</t>
+          <t>47833</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35117</t>
+          <t>37698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56246</t>
+          <t>59947</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>87796</t>
+          <t>89233</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72126</t>
+          <t>72697</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109378</t>
+          <t>109618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82085</t>
+          <t>83485</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63413</t>
+          <t>65697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99915</t>
+          <t>101948</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>81898</t>
+          <t>89080</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71056</t>
+          <t>78318</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94132</t>
+          <t>100515</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>163983</t>
+          <t>172566</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142103</t>
+          <t>150974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185356</t>
+          <t>191978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66120</t>
+          <t>66990</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51925</t>
+          <t>51876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82806</t>
+          <t>83160</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>40249</t>
+          <t>40046</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31933</t>
+          <t>31030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51015</t>
+          <t>50670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>106369</t>
+          <t>107036</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87615</t>
+          <t>89425</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125969</t>
+          <t>124919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>11919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>10892</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,22 +1816,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17109</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>197856</t>
+          <t>198346</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>197856</t>
+          <t>198346</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>197856</t>
+          <t>198346</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181550</t>
+          <t>192406</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181550</t>
+          <t>192406</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181550</t>
+          <t>192406</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>379406</t>
+          <t>390752</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>379406</t>
+          <t>390752</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>379406</t>
+          <t>390752</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14018</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>20985</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42404</t>
+          <t>43577</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33198</t>
+          <t>33639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52421</t>
+          <t>53045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>54751</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43570</t>
+          <t>45382</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61719</t>
+          <t>64404</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>94414</t>
+          <t>98327</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81399</t>
+          <t>84305</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108146</t>
+          <t>112238</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>59800</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45290</t>
+          <t>49076</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67474</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46117</t>
+          <t>47555</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37095</t>
+          <t>39302</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55303</t>
+          <t>57566</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>102701</t>
+          <t>107355</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>88088</t>
+          <t>91376</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>117860</t>
+          <t>121175</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20724</t>
+          <t>20646</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>28110</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>14167</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>30044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16951</t>
+          <t>18450</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>12827</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>26555</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>36356</t>
+          <t>38735</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26702</t>
+          <t>29374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45642</t>
+          <t>49569</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>134050</t>
+          <t>138883</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>134050</t>
+          <t>138883</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>134050</t>
+          <t>138883</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>134327</t>
+          <t>139961</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>134327</t>
+          <t>139961</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>134327</t>
+          <t>139961</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>268377</t>
+          <t>278844</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>268377</t>
+          <t>278844</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>268377</t>
+          <t>278844</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>27477</t>
+          <t>26814</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46430</t>
+          <t>44142</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33715</t>
+          <t>36358</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25706</t>
+          <t>27114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46069</t>
+          <t>48650</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>61191</t>
+          <t>63172</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45440</t>
+          <t>47857</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84632</t>
+          <t>85524</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>19205</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32760</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35568</t>
+          <t>41757</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26888</t>
+          <t>30808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49228</t>
+          <t>54434</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>56898</t>
+          <t>73095</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44455</t>
+          <t>57055</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75891</t>
+          <t>92898</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>34167</t>
+          <t>41398</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22722</t>
+          <t>29377</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47630</t>
+          <t>57884</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20936</t>
+          <t>23911</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28664</t>
+          <t>32073</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>55103</t>
+          <t>65309</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41290</t>
+          <t>50561</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71899</t>
+          <t>83631</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14597</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>33008</t>
+          <t>36111</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22727</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45257</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>51127</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34632</t>
+          <t>41080</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55459</t>
+          <t>63440</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>76890</t>
+          <t>87239</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63512</t>
+          <t>72308</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>93904</t>
+          <t>106568</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>116864</t>
+          <t>137125</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>116864</t>
+          <t>137125</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>116864</t>
+          <t>137125</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>140831</t>
+          <t>160634</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>140831</t>
+          <t>160634</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>140831</t>
+          <t>160634</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>257695</t>
+          <t>297760</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>257695</t>
+          <t>297760</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>257695</t>
+          <t>297760</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>383</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>388</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13422</t>
+          <t>15733</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>23849</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26511</t>
+          <t>29395</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>30107</t>
+          <t>33653</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>24384</t>
+          <t>26244</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>38016</t>
+          <t>40526</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>34616</t>
+          <t>38503</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29828</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38631</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>45193</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37406</t>
+          <t>39204</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>47506</t>
+          <t>50588</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>77023</t>
+          <t>83697</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>69253</t>
+          <t>76277</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>83725</t>
+          <t>91645</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>558</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>867</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,22 +3975,22 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>388</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>66354</t>
+          <t>71458</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>66354</t>
+          <t>71458</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>66354</t>
+          <t>71458</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>111296</t>
+          <t>121763</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>111296</t>
+          <t>121763</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>111296</t>
+          <t>121763</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>467</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>240</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,22 +4205,22 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>553</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>37398</t>
+          <t>39855</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>28823</t>
+          <t>31512</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>47232</t>
+          <t>49558</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>38493</t>
+          <t>40676</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>30550</t>
+          <t>32695</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>46483</t>
+          <t>49713</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>75891</t>
+          <t>80530</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>64636</t>
+          <t>69099</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>88367</t>
+          <t>93812</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>48643</t>
+          <t>46948</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>39592</t>
+          <t>37065</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>59025</t>
+          <t>55910</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>51699</t>
+          <t>51997</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>43208</t>
+          <t>43734</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>61670</t>
+          <t>61123</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>100342</t>
+          <t>98945</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>87311</t>
+          <t>86174</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>112921</t>
+          <t>111883</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>22755</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>15268</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>23455</t>
+          <t>23729</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>17714</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>27663</t>
+          <t>27154</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>20415</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>37055</t>
+          <t>36346</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>109356</t>
+          <t>109284</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>109356</t>
+          <t>109284</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>109356</t>
+          <t>109284</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>112331</t>
+          <t>114924</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>112331</t>
+          <t>114924</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>112331</t>
+          <t>114924</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>221687</t>
+          <t>224207</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>221687</t>
+          <t>224207</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>221687</t>
+          <t>224207</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>31587</t>
+          <t>31137</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18982</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>49978</t>
+          <t>47613</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>14116</t>
+          <t>20395</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>33906</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>45703</t>
+          <t>51532</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>37599</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>79738</t>
+          <t>71139</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>32206</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>22539</t>
+          <t>28205</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>45902</t>
+          <t>54591</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>251362</t>
+          <t>58027</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>88246</t>
+          <t>47846</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>352706</t>
+          <t>70411</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>283568</t>
+          <t>97934</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>112636</t>
+          <t>81480</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>473798</t>
+          <t>116874</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>90914</t>
+          <t>98673</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>73667</t>
+          <t>82923</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>109111</t>
+          <t>115970</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>90286</t>
+          <t>105520</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>25572</t>
+          <t>90826</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>193985</t>
+          <t>118739</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>181200</t>
+          <t>204192</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>67136</t>
+          <t>183556</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>288686</t>
+          <t>225939</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>50,4%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>27987</t>
+          <t>30103</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>42712</t>
+          <t>44967</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>28432</t>
+          <t>31834</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>67123</t>
+          <t>43239</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>56419</t>
+          <t>61937</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>21254</t>
+          <t>48690</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>94468</t>
+          <t>79103</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>12764</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>29221</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>15994</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>10517</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>27952</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>23106</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>42969</t>
+          <t>45367</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>195458</t>
+          <t>216509</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>195458</t>
+          <t>216509</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>195458</t>
+          <t>216509</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>395640</t>
+          <t>231770</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>395640</t>
+          <t>231770</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>395640</t>
+          <t>231770</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>591098</t>
+          <t>448278</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>591098</t>
+          <t>448278</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>591098</t>
+          <t>448278</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>10574</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>42299</t>
+          <t>53532</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>31031</t>
+          <t>39738</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>56064</t>
+          <t>70672</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>56290</t>
+          <t>68539</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>45153</t>
+          <t>54670</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>69453</t>
+          <t>84888</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>98589</t>
+          <t>122071</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>81224</t>
+          <t>102027</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>116872</t>
+          <t>142744</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>75813</t>
+          <t>85987</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>62055</t>
+          <t>71498</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>90711</t>
+          <t>103801</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>64470</t>
+          <t>73563</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>53047</t>
+          <t>59908</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>77459</t>
+          <t>86293</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>140283</t>
+          <t>159550</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>122153</t>
+          <t>138800</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>157771</t>
+          <t>181368</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>120674</t>
+          <t>140803</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>103335</t>
+          <t>122780</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>136112</t>
+          <t>160902</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>113183</t>
+          <t>128777</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>99360</t>
+          <t>113362</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>128233</t>
+          <t>146508</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>233856</t>
+          <t>269580</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>213442</t>
+          <t>245216</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>256889</t>
+          <t>294971</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>42503</t>
+          <t>51925</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>33029</t>
+          <t>40204</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>54724</t>
+          <t>66302</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>65848</t>
+          <t>75540</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>54208</t>
+          <t>61445</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>78377</t>
+          <t>90651</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>108351</t>
+          <t>127465</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>91403</t>
+          <t>108478</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>124491</t>
+          <t>147668</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>283970</t>
+          <t>335232</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>283970</t>
+          <t>335232</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>283970</t>
+          <t>335232</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>300655</t>
+          <t>348152</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>300655</t>
+          <t>348152</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>300655</t>
+          <t>348152</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>584625</t>
+          <t>683384</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>584625</t>
+          <t>683384</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>584625</t>
+          <t>683384</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>118610</t>
+          <t>113722</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>91765</t>
+          <t>89377</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>155621</t>
+          <t>145069</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>105088</t>
+          <t>118456</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>63278</t>
+          <t>100858</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>130316</t>
+          <t>140174</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
           <t>7,15%</t>
         </is>
       </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>223698</t>
+          <t>232178</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>167890</t>
+          <t>200512</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>269705</t>
+          <t>266867</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>285861</t>
+          <t>337909</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>255865</t>
+          <t>307497</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>320243</t>
+          <t>376985</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>587670</t>
+          <t>438715</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>433599</t>
+          <t>407506</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>927840</t>
+          <t>467763</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>873531</t>
+          <t>776625</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>709056</t>
+          <t>732929</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1349015</t>
+          <t>825430</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>475019</t>
+          <t>505249</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>439416</t>
+          <t>468699</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>515582</t>
+          <t>542651</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>422483</t>
+          <t>455357</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>261939</t>
+          <t>426477</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>500321</t>
+          <t>484250</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>897502</t>
+          <t>960606</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>655904</t>
+          <t>912501</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>984342</t>
+          <t>1006880</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>191683</t>
+          <t>211138</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>166042</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>217935</t>
+          <t>241575</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>185868</t>
+          <t>205796</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>111900</t>
+          <t>183257</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>225418</t>
+          <t>228537</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>377551</t>
+          <t>416934</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>276518</t>
+          <t>379491</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>424557</t>
+          <t>452488</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -6633,27 +6633,27 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>137852</t>
+          <t>154408</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>117195</t>
+          <t>133391</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>162978</t>
+          <t>178212</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>169115</t>
+          <t>192161</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>102194</t>
+          <t>171088</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>205036</t>
+          <t>215672</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>306967</t>
+          <t>346569</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>229033</t>
+          <t>315136</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>346830</t>
+          <t>377139</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>1209025</t>
+          <t>1322427</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>1209025</t>
+          <t>1322427</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1209025</t>
+          <t>1322427</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>1470224</t>
+          <t>1410484</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>1470224</t>
+          <t>1410484</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>1470224</t>
+          <t>1410484</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>2679249</t>
+          <t>2732911</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>2679249</t>
+          <t>2732911</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>2679249</t>
+          <t>2732911</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
